--- a/Oh_Chewy_Cookie_Cost_Calculator.xlsx
+++ b/Oh_Chewy_Cookie_Cost_Calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tahaluf-my.sharepoint.com/personal/o_badawi_ext_tahaluf_ae/Documents/Desktop/cookies/Oh-Chewy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{7004D838-7F5F-48E7-8195-CA2C48C79446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A1995E6-9366-448E-B52D-70379CF21E53}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{56562527-23F4-4E6A-A6F1-190B3297969D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E9F6FC4-F9C5-4668-9857-2FE9E671460C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1141,7 +1141,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
